--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -56,9 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,12 +541,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>NUCLEAR_MW</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>GAS_MW</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>HYDRO_MW</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>WIND_MW</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SOLAR_MW</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>BIOFUEL_MW</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>OTHER_MW</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Total_MW</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Renewables_Share</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Hours_Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2" t="n">
+        <v>7590.454545454545</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5436.409090909091</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3287.727272727273</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1516.772727272727</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52.59090909090909</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>101.7727272727273</v>
+      </c>
+      <c r="I2" t="n">
+        <v>17985.72727272727</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2700525163892581</v>
+      </c>
+      <c r="K2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -609,34 +609,34 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>7590.454545454545</v>
+        <v>7583.304347826087</v>
       </c>
       <c r="C2" t="n">
-        <v>5436.409090909091</v>
+        <v>5435.782608695652</v>
       </c>
       <c r="D2" t="n">
-        <v>3287.727272727273</v>
+        <v>3276.260869565217</v>
       </c>
       <c r="E2" t="n">
-        <v>1516.772727272727</v>
+        <v>1543.652173913043</v>
       </c>
       <c r="F2" t="n">
-        <v>52.59090909090909</v>
+        <v>50.30434782608695</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>101.7727272727273</v>
+        <v>97.39130434782609</v>
       </c>
       <c r="I2" t="n">
-        <v>17985.72727272727</v>
+        <v>17986.69565217392</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2700525163892581</v>
+        <v>0.270767765546515</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -59,11 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -138,6 +142,425 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>canada_ieso_generation_daily - Data (to Oct/26)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart'!$J$2:$J$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$B$2:$B$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart'!$J$2:$J$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$C$2:$C$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart'!$J$2:$J$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$D$2:$D$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="EDA100"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart'!$J$2:$J$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$E$2:$E$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E87BA4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart'!$J$2:$J$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$F$2:$F$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="008300"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart'!$J$2:$J$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$G$2:$G$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="4A3AA7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart'!$J$2:$J$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$H$2:$H$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart'!$J$2:$J$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$I$2:$I$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10080000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,7 +879,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -485,7 +907,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -500,7 +921,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -515,7 +935,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
@@ -541,7 +960,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>NUCLEAR_MW</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>GAS_MW</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>HYDRO_MW</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>WIND_MW</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SOLAR_MW</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>BIOFUEL_MW</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>OTHER_MW</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Total_MW</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2" t="n">
+        <v>7583.304347826087</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5435.782608695652</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3276.260869565217</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1543.652173913043</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50.30434782608695</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>97.39130434782609</v>
+      </c>
+      <c r="I2" t="n">
+        <v>17986.69565217392</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sep/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7390.181818181818</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5485.454545454545</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3413.954545454545</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1789.045454545455</v>
+      </c>
+      <c r="F3" t="n">
+        <v>28.72727272727273</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18233.86363636364</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Oct/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -639,6 +1196,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7390.181818181818</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5485.454545454545</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3413.954545454545</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1789.045454545455</v>
+      </c>
+      <c r="F3" t="n">
+        <v>28.72727272727273</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18233.86363636364</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2869236809632427</v>
+      </c>
+      <c r="K3" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1057,28 +1057,28 @@
         <v>46296</v>
       </c>
       <c r="B3" t="n">
-        <v>7390.181818181818</v>
+        <v>7388.782608695652</v>
       </c>
       <c r="C3" t="n">
-        <v>5485.454545454545</v>
+        <v>5504.478260869565</v>
       </c>
       <c r="D3" t="n">
-        <v>3413.954545454545</v>
+        <v>3407.217391304348</v>
       </c>
       <c r="E3" t="n">
-        <v>1789.045454545455</v>
+        <v>1757.869565217391</v>
       </c>
       <c r="F3" t="n">
-        <v>28.72727272727273</v>
+        <v>27.47826086956522</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>126.5</v>
+        <v>132.8260869565217</v>
       </c>
       <c r="I3" t="n">
-        <v>18233.86363636364</v>
+        <v>18218.65217391304</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         <v>46296</v>
       </c>
       <c r="B3" t="n">
-        <v>7390.181818181818</v>
+        <v>7388.782608695652</v>
       </c>
       <c r="C3" t="n">
-        <v>5485.454545454545</v>
+        <v>5504.478260869565</v>
       </c>
       <c r="D3" t="n">
-        <v>3413.954545454545</v>
+        <v>3407.217391304348</v>
       </c>
       <c r="E3" t="n">
-        <v>1789.045454545455</v>
+        <v>1757.869565217391</v>
       </c>
       <c r="F3" t="n">
-        <v>28.72727272727273</v>
+        <v>27.47826086956522</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>126.5</v>
+        <v>132.8260869565217</v>
       </c>
       <c r="I3" t="n">
-        <v>18233.86363636364</v>
+        <v>18218.65217391304</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2869236809632427</v>
+        <v>0.2850136864035664</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$3</f>
+              <f>'Chart'!$J$2:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$3</f>
+              <f>'Chart'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$3</f>
+              <f>'Chart'!$J$2:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$3</f>
+              <f>'Chart'!$C$2:$C$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$3</f>
+              <f>'Chart'!$J$2:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$3</f>
+              <f>'Chart'!$D$2:$D$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$3</f>
+              <f>'Chart'!$J$2:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$3</f>
+              <f>'Chart'!$E$2:$E$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$3</f>
+              <f>'Chart'!$J$2:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$3</f>
+              <f>'Chart'!$F$2:$F$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -372,12 +372,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$3</f>
+              <f>'Chart'!$J$2:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$3</f>
+              <f>'Chart'!$G$2:$G$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -408,12 +408,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$3</f>
+              <f>'Chart'!$J$2:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$3</f>
+              <f>'Chart'!$H$2:$H$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$3</f>
+              <f>'Chart'!$J$2:$J$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$3</f>
+              <f>'Chart'!$I$2:$I$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1084,6 +1084,35 @@
         <is>
           <t>Oct/26</t>
         </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7365.05</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5503.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3240.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1580.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17880.65</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1231,6 +1260,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7365.05</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5503.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3240.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1580.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17880.65</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2736729369458046</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1091,28 +1091,28 @@
         <v>46297</v>
       </c>
       <c r="B4" t="n">
-        <v>7365.05</v>
+        <v>7366.090909090909</v>
       </c>
       <c r="C4" t="n">
-        <v>5503.3</v>
+        <v>5537.409090909091</v>
       </c>
       <c r="D4" t="n">
-        <v>3240.5</v>
+        <v>3257.727272727273</v>
       </c>
       <c r="E4" t="n">
-        <v>1580.1</v>
+        <v>1544.545454545455</v>
       </c>
       <c r="F4" t="n">
-        <v>72.84999999999999</v>
+        <v>66.22727272727273</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>118.85</v>
+        <v>120.2272727272727</v>
       </c>
       <c r="I4" t="n">
-        <v>17880.65</v>
+        <v>17892.22727272727</v>
       </c>
     </row>
   </sheetData>
@@ -1265,34 +1265,34 @@
         <v>46297</v>
       </c>
       <c r="B4" t="n">
-        <v>7365.05</v>
+        <v>7366.090909090909</v>
       </c>
       <c r="C4" t="n">
-        <v>5503.3</v>
+        <v>5537.409090909091</v>
       </c>
       <c r="D4" t="n">
-        <v>3240.5</v>
+        <v>3257.727272727273</v>
       </c>
       <c r="E4" t="n">
-        <v>1580.1</v>
+        <v>1544.545454545455</v>
       </c>
       <c r="F4" t="n">
-        <v>72.84999999999999</v>
+        <v>66.22727272727273</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>118.85</v>
+        <v>120.2272727272727</v>
       </c>
       <c r="I4" t="n">
-        <v>17880.65</v>
+        <v>17892.22727272727</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2736729369458046</v>
+        <v>0.2721013949683586</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1091,28 +1091,28 @@
         <v>46297</v>
       </c>
       <c r="B4" t="n">
-        <v>7366.090909090909</v>
+        <v>7366.869565217391</v>
       </c>
       <c r="C4" t="n">
-        <v>5537.409090909091</v>
+        <v>5546.869565217391</v>
       </c>
       <c r="D4" t="n">
-        <v>3257.727272727273</v>
+        <v>3247.565217391304</v>
       </c>
       <c r="E4" t="n">
-        <v>1544.545454545455</v>
+        <v>1518.391304347826</v>
       </c>
       <c r="F4" t="n">
-        <v>66.22727272727273</v>
+        <v>63.34782608695652</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>120.2272727272727</v>
+        <v>115.5652173913043</v>
       </c>
       <c r="I4" t="n">
-        <v>17892.22727272727</v>
+        <v>17858.60869565217</v>
       </c>
     </row>
   </sheetData>
@@ -1265,34 +1265,34 @@
         <v>46297</v>
       </c>
       <c r="B4" t="n">
-        <v>7366.090909090909</v>
+        <v>7366.869565217391</v>
       </c>
       <c r="C4" t="n">
-        <v>5537.409090909091</v>
+        <v>5546.869565217391</v>
       </c>
       <c r="D4" t="n">
-        <v>3257.727272727273</v>
+        <v>3247.565217391304</v>
       </c>
       <c r="E4" t="n">
-        <v>1544.545454545455</v>
+        <v>1518.391304347826</v>
       </c>
       <c r="F4" t="n">
-        <v>66.22727272727273</v>
+        <v>63.34782608695652</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>120.2272727272727</v>
+        <v>115.5652173913043</v>
       </c>
       <c r="I4" t="n">
-        <v>17892.22727272727</v>
+        <v>17858.60869565217</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2721013949683586</v>
+        <v>0.270418845618238</v>
       </c>
       <c r="K4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4</f>
+              <f>'Chart'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4</f>
+              <f>'Chart'!$C$2:$C$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$4</f>
+              <f>'Chart'!$D$2:$D$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$4</f>
+              <f>'Chart'!$E$2:$E$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$4</f>
+              <f>'Chart'!$F$2:$F$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -372,12 +372,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$4</f>
+              <f>'Chart'!$G$2:$G$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -408,12 +408,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$4</f>
+              <f>'Chart'!$H$2:$H$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$4</f>
+              <f>'Chart'!$J$2:$J$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$4</f>
+              <f>'Chart'!$I$2:$I$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1113,6 +1113,35 @@
       </c>
       <c r="I4" t="n">
         <v>17858.60869565217</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7408.041666666667</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4537.25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3133.208333333333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>523.9166666666666</v>
+      </c>
+      <c r="F5" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>117.2083333333333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15847.375</v>
       </c>
     </row>
   </sheetData>
@@ -1127,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1295,6 +1324,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7408.041666666667</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4537.25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3133.208333333333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>523.9166666666666</v>
+      </c>
+      <c r="F5" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>117.2083333333333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15847.375</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.238832929743885</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$5</f>
+              <f>'Chart'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$5</f>
+              <f>'Chart'!$C$2:$C$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$5</f>
+              <f>'Chart'!$D$2:$D$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$5</f>
+              <f>'Chart'!$F$2:$F$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -372,12 +372,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$5</f>
+              <f>'Chart'!$G$2:$G$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -408,12 +408,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$5</f>
+              <f>'Chart'!$H$2:$H$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$5</f>
+              <f>'Chart'!$J$2:$J$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$5</f>
+              <f>'Chart'!$I$2:$I$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1142,6 +1142,35 @@
       </c>
       <c r="I5" t="n">
         <v>15847.375</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7402.090909090909</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3823.090909090909</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3193.545454545455</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1792.636363636364</v>
+      </c>
+      <c r="F6" t="n">
+        <v>82.13636363636364</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>106.4090909090909</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16399.90909090909</v>
       </c>
     </row>
   </sheetData>
@@ -1156,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1359,6 +1388,41 @@
         <v>24</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7402.090909090909</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3823.090909090909</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3193.545454545455</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1792.636363636364</v>
+      </c>
+      <c r="F6" t="n">
+        <v>82.13636363636364</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>106.4090909090909</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16399.90909090909</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3090455046868331</v>
+      </c>
+      <c r="K6" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1149,28 +1149,28 @@
         <v>46299</v>
       </c>
       <c r="B6" t="n">
-        <v>7402.090909090909</v>
+        <v>7401.608695652174</v>
       </c>
       <c r="C6" t="n">
-        <v>3823.090909090909</v>
+        <v>3821.130434782609</v>
       </c>
       <c r="D6" t="n">
-        <v>3193.545454545455</v>
+        <v>3183.130434782609</v>
       </c>
       <c r="E6" t="n">
-        <v>1792.636363636364</v>
+        <v>1813.782608695652</v>
       </c>
       <c r="F6" t="n">
-        <v>82.13636363636364</v>
+        <v>78.56521739130434</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>106.4090909090909</v>
+        <v>101.7826086956522</v>
       </c>
       <c r="I6" t="n">
-        <v>16399.90909090909</v>
+        <v>16400</v>
       </c>
     </row>
   </sheetData>
@@ -1393,34 +1393,34 @@
         <v>46299</v>
       </c>
       <c r="B6" t="n">
-        <v>7402.090909090909</v>
+        <v>7401.608695652174</v>
       </c>
       <c r="C6" t="n">
-        <v>3823.090909090909</v>
+        <v>3821.130434782609</v>
       </c>
       <c r="D6" t="n">
-        <v>3193.545454545455</v>
+        <v>3183.130434782609</v>
       </c>
       <c r="E6" t="n">
-        <v>1792.636363636364</v>
+        <v>1813.782608695652</v>
       </c>
       <c r="F6" t="n">
-        <v>82.13636363636364</v>
+        <v>78.56521739130434</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>106.4090909090909</v>
+        <v>101.7826086956522</v>
       </c>
       <c r="I6" t="n">
-        <v>16399.90909090909</v>
+        <v>16400</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3090455046868331</v>
+        <v>0.3094803817603393</v>
       </c>
       <c r="K6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$6</f>
+              <f>'Chart'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$6</f>
+              <f>'Chart'!$C$2:$C$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$6</f>
+              <f>'Chart'!$D$2:$D$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$6</f>
+              <f>'Chart'!$E$2:$E$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$6</f>
+              <f>'Chart'!$F$2:$F$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -372,12 +372,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$6</f>
+              <f>'Chart'!$G$2:$G$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -408,12 +408,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$6</f>
+              <f>'Chart'!$H$2:$H$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$6</f>
+              <f>'Chart'!$J$2:$J$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1171,6 +1171,35 @@
       </c>
       <c r="I6" t="n">
         <v>16400</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7405.090909090909</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3704.090909090909</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3323.954545454545</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2259.227272727273</v>
+      </c>
+      <c r="F7" t="n">
+        <v>116</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>112.7272727272727</v>
+      </c>
+      <c r="I7" t="n">
+        <v>16921.09090909091</v>
       </c>
     </row>
   </sheetData>
@@ -1185,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1423,6 +1452,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7405.090909090909</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3704.090909090909</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3323.954545454545</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2259.227272727273</v>
+      </c>
+      <c r="F7" t="n">
+        <v>116</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>112.7272727272727</v>
+      </c>
+      <c r="I7" t="n">
+        <v>16921.09090909091</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3368093610985752</v>
+      </c>
+      <c r="K7" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1178,28 +1178,28 @@
         <v>46300</v>
       </c>
       <c r="B7" t="n">
-        <v>7405.090909090909</v>
+        <v>7409.739130434783</v>
       </c>
       <c r="C7" t="n">
-        <v>3704.090909090909</v>
+        <v>3751.04347826087</v>
       </c>
       <c r="D7" t="n">
-        <v>3323.954545454545</v>
+        <v>3317.826086956522</v>
       </c>
       <c r="E7" t="n">
-        <v>2259.227272727273</v>
+        <v>2190.04347826087</v>
       </c>
       <c r="F7" t="n">
-        <v>116</v>
+        <v>110.9565217391304</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>112.7272727272727</v>
+        <v>113.2608695652174</v>
       </c>
       <c r="I7" t="n">
-        <v>16921.09090909091</v>
+        <v>16892.86956521739</v>
       </c>
     </row>
   </sheetData>
@@ -1457,34 +1457,34 @@
         <v>46300</v>
       </c>
       <c r="B7" t="n">
-        <v>7405.090909090909</v>
+        <v>7409.739130434783</v>
       </c>
       <c r="C7" t="n">
-        <v>3704.090909090909</v>
+        <v>3751.04347826087</v>
       </c>
       <c r="D7" t="n">
-        <v>3323.954545454545</v>
+        <v>3317.826086956522</v>
       </c>
       <c r="E7" t="n">
-        <v>2259.227272727273</v>
+        <v>2190.04347826087</v>
       </c>
       <c r="F7" t="n">
-        <v>116</v>
+        <v>110.9565217391304</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>112.7272727272727</v>
+        <v>113.2608695652174</v>
       </c>
       <c r="I7" t="n">
-        <v>16921.09090909091</v>
+        <v>16892.86956521739</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3368093610985752</v>
+        <v>0.3326152531554347</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$7</f>
+              <f>'Chart'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$7</f>
+              <f>'Chart'!$C$2:$C$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$7</f>
+              <f>'Chart'!$D$2:$D$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$7</f>
+              <f>'Chart'!$E$2:$E$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$7</f>
+              <f>'Chart'!$F$2:$F$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -372,12 +372,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$7</f>
+              <f>'Chart'!$G$2:$G$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -408,12 +408,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$7</f>
+              <f>'Chart'!$H$2:$H$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$7</f>
+              <f>'Chart'!$J$2:$J$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$7</f>
+              <f>'Chart'!$I$2:$I$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1200,6 +1200,35 @@
       </c>
       <c r="I7" t="n">
         <v>16892.86956521739</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7511.954545454545</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4193.272727272727</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3346.272727272727</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1146.227272727273</v>
+      </c>
+      <c r="F8" t="n">
+        <v>135.6363636363636</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>120.9090909090909</v>
+      </c>
+      <c r="I8" t="n">
+        <v>16454.27272727273</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +1243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1487,6 +1516,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7511.954545454545</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4193.272727272727</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3346.272727272727</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1146.227272727273</v>
+      </c>
+      <c r="F8" t="n">
+        <v>135.6363636363636</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>120.9090909090909</v>
+      </c>
+      <c r="I8" t="n">
+        <v>16454.27272727273</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2812726177781952</v>
+      </c>
+      <c r="K8" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1207,28 +1207,28 @@
         <v>46301</v>
       </c>
       <c r="B8" t="n">
-        <v>7511.954545454545</v>
+        <v>7511.913043478261</v>
       </c>
       <c r="C8" t="n">
-        <v>4193.272727272727</v>
+        <v>4164.695652173913</v>
       </c>
       <c r="D8" t="n">
-        <v>3346.272727272727</v>
+        <v>3330.95652173913</v>
       </c>
       <c r="E8" t="n">
-        <v>1146.227272727273</v>
+        <v>1234.260869565217</v>
       </c>
       <c r="F8" t="n">
-        <v>135.6363636363636</v>
+        <v>129.7391304347826</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>120.9090909090909</v>
+        <v>116.3478260869565</v>
       </c>
       <c r="I8" t="n">
-        <v>16454.27272727273</v>
+        <v>16487.91304347826</v>
       </c>
     </row>
   </sheetData>
@@ -1521,34 +1521,34 @@
         <v>46301</v>
       </c>
       <c r="B8" t="n">
-        <v>7511.954545454545</v>
+        <v>7511.913043478261</v>
       </c>
       <c r="C8" t="n">
-        <v>4193.272727272727</v>
+        <v>4164.695652173913</v>
       </c>
       <c r="D8" t="n">
-        <v>3346.272727272727</v>
+        <v>3330.95652173913</v>
       </c>
       <c r="E8" t="n">
-        <v>1146.227272727273</v>
+        <v>1234.260869565217</v>
       </c>
       <c r="F8" t="n">
-        <v>135.6363636363636</v>
+        <v>129.7391304347826</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>120.9090909090909</v>
+        <v>116.3478260869565</v>
       </c>
       <c r="I8" t="n">
-        <v>16454.27272727273</v>
+        <v>16487.91304347826</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2812726177781952</v>
+        <v>0.2847514121016186</v>
       </c>
       <c r="K8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$8</f>
+              <f>'Chart'!$J$2:$J$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$8</f>
+              <f>'Chart'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$8</f>
+              <f>'Chart'!$J$2:$J$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$8</f>
+              <f>'Chart'!$C$2:$C$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$8</f>
+              <f>'Chart'!$J$2:$J$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$8</f>
+              <f>'Chart'!$D$2:$D$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -300,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$8</f>
+              <f>'Chart'!$J$2:$J$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$8</f>
+              <f>'Chart'!$E$2:$E$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -336,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$8</f>
+              <f>'Chart'!$J$2:$J$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$8</f>
+              <f>'Chart'!$F$2:$F$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -372,12 +372,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$8</f>
+              <f>'Chart'!$J$2:$J$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$8</f>
+              <f>'Chart'!$G$2:$G$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -408,12 +408,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$8</f>
+              <f>'Chart'!$J$2:$J$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$8</f>
+              <f>'Chart'!$H$2:$H$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$8</f>
+              <f>'Chart'!$J$2:$J$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$8</f>
+              <f>'Chart'!$I$2:$I$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1229,6 +1229,35 @@
       </c>
       <c r="I8" t="n">
         <v>16487.91304347826</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7517.818181818182</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3644.363636363636</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3428.045454545455</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2759</v>
+      </c>
+      <c r="F9" t="n">
+        <v>88.22727272727273</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17620.72727272727</v>
       </c>
     </row>
   </sheetData>
@@ -1243,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1551,6 +1580,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7517.818181818182</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3644.363636363636</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3428.045454545455</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2759</v>
+      </c>
+      <c r="F9" t="n">
+        <v>88.22727272727273</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17620.72727272727</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3561301772705698</v>
+      </c>
+      <c r="K9" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -177,7 +177,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="008300"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -249,7 +249,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -285,7 +285,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="EDA100"/>
+                <a:srgbClr val="1BAF7A"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -321,7 +321,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="E87BA4"/>
+                <a:srgbClr val="EDA100"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -393,7 +393,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="4A3AA7"/>
+                <a:srgbClr val="9A9A9A"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1236,28 +1236,28 @@
         <v>46302</v>
       </c>
       <c r="B9" t="n">
-        <v>7517.818181818182</v>
+        <v>7517.217391304348</v>
       </c>
       <c r="C9" t="n">
-        <v>3644.363636363636</v>
+        <v>3663.434782608696</v>
       </c>
       <c r="D9" t="n">
-        <v>3428.045454545455</v>
+        <v>3417.608695652174</v>
       </c>
       <c r="E9" t="n">
-        <v>2759</v>
+        <v>2735.652173913043</v>
       </c>
       <c r="F9" t="n">
-        <v>88.22727272727273</v>
+        <v>84.39130434782609</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>183.2727272727273</v>
+        <v>175.5652173913043</v>
       </c>
       <c r="I9" t="n">
-        <v>17620.72727272727</v>
+        <v>17593.86956521739</v>
       </c>
     </row>
   </sheetData>
@@ -1585,34 +1585,34 @@
         <v>46302</v>
       </c>
       <c r="B9" t="n">
-        <v>7517.818181818182</v>
+        <v>7517.217391304348</v>
       </c>
       <c r="C9" t="n">
-        <v>3644.363636363636</v>
+        <v>3663.434782608696</v>
       </c>
       <c r="D9" t="n">
-        <v>3428.045454545455</v>
+        <v>3417.608695652174</v>
       </c>
       <c r="E9" t="n">
-        <v>2759</v>
+        <v>2735.652173913043</v>
       </c>
       <c r="F9" t="n">
-        <v>88.22727272727273</v>
+        <v>84.39130434782609</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>183.2727272727273</v>
+        <v>175.5652173913043</v>
       </c>
       <c r="I9" t="n">
-        <v>17620.72727272727</v>
+        <v>17593.86956521739</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3561301772705698</v>
+        <v>0.354535547213827</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>canada_ieso_generation_daily - Data (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -192,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$9</f>
+              <f>'Chart'!$J$2:$J$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$9</f>
+              <f>'Chart'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +229,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$9</f>
+              <f>'Chart'!$J$2:$J$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$9</f>
+              <f>'Chart'!$C$2:$C$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +265,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$9</f>
+              <f>'Chart'!$J$2:$J$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$9</f>
+              <f>'Chart'!$D$2:$D$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -300,12 +301,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$9</f>
+              <f>'Chart'!$J$2:$J$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$9</f>
+              <f>'Chart'!$E$2:$E$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -336,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$9</f>
+              <f>'Chart'!$J$2:$J$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$9</f>
+              <f>'Chart'!$F$2:$F$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -372,12 +373,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$9</f>
+              <f>'Chart'!$J$2:$J$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$9</f>
+              <f>'Chart'!$G$2:$G$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -408,12 +409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$9</f>
+              <f>'Chart'!$J$2:$J$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$9</f>
+              <f>'Chart'!$H$2:$H$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -444,12 +445,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$9</f>
+              <f>'Chart'!$J$2:$J$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$9</f>
+              <f>'Chart'!$I$2:$I$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -960,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1258,6 +1259,35 @@
       </c>
       <c r="I9" t="n">
         <v>17593.86956521739</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7520.545454545455</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4293.363636363636</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3375.681818181818</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1927.954545454545</v>
+      </c>
+      <c r="F10" t="n">
+        <v>97.86363636363636</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>175.4090909090909</v>
+      </c>
+      <c r="I10" t="n">
+        <v>17390.81818181818</v>
       </c>
     </row>
   </sheetData>
@@ -1272,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1615,6 +1645,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7520.545454545455</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4293.363636363636</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3375.681818181818</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1927.954545454545</v>
+      </c>
+      <c r="F10" t="n">
+        <v>97.86363636363636</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>175.4090909090909</v>
+      </c>
+      <c r="I10" t="n">
+        <v>17390.81818181818</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3105949325401596</v>
+      </c>
+      <c r="K10" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1266,28 +1266,28 @@
         <v>46303</v>
       </c>
       <c r="B10" t="n">
-        <v>7520.545454545455</v>
+        <v>7520.478260869565</v>
       </c>
       <c r="C10" t="n">
-        <v>4293.363636363636</v>
+        <v>4306.521739130435</v>
       </c>
       <c r="D10" t="n">
-        <v>3375.681818181818</v>
+        <v>3355.260869565217</v>
       </c>
       <c r="E10" t="n">
-        <v>1927.954545454545</v>
+        <v>1915.608695652174</v>
       </c>
       <c r="F10" t="n">
-        <v>97.86363636363636</v>
+        <v>93.60869565217391</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>175.4090909090909</v>
+        <v>171.0869565217391</v>
       </c>
       <c r="I10" t="n">
-        <v>17390.81818181818</v>
+        <v>17362.5652173913</v>
       </c>
     </row>
   </sheetData>
@@ -1650,34 +1650,34 @@
         <v>46303</v>
       </c>
       <c r="B10" t="n">
-        <v>7520.545454545455</v>
+        <v>7520.478260869565</v>
       </c>
       <c r="C10" t="n">
-        <v>4293.363636363636</v>
+        <v>4306.521739130435</v>
       </c>
       <c r="D10" t="n">
-        <v>3375.681818181818</v>
+        <v>3355.260869565217</v>
       </c>
       <c r="E10" t="n">
-        <v>1927.954545454545</v>
+        <v>1915.608695652174</v>
       </c>
       <c r="F10" t="n">
-        <v>97.86363636363636</v>
+        <v>93.60869565217391</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>175.4090909090909</v>
+        <v>171.0869565217391</v>
       </c>
       <c r="I10" t="n">
-        <v>17390.81818181818</v>
+        <v>17362.5652173913</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3105949325401596</v>
+        <v>0.3089680697352375</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -193,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$10</f>
+              <f>'Chart'!$J$2:$J$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$10</f>
+              <f>'Chart'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -229,12 +229,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$10</f>
+              <f>'Chart'!$J$2:$J$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$10</f>
+              <f>'Chart'!$C$2:$C$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -265,12 +265,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$10</f>
+              <f>'Chart'!$J$2:$J$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$10</f>
+              <f>'Chart'!$D$2:$D$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -301,12 +301,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$10</f>
+              <f>'Chart'!$J$2:$J$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$10</f>
+              <f>'Chart'!$E$2:$E$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -337,12 +337,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$10</f>
+              <f>'Chart'!$J$2:$J$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$10</f>
+              <f>'Chart'!$F$2:$F$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -373,12 +373,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$10</f>
+              <f>'Chart'!$J$2:$J$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$10</f>
+              <f>'Chart'!$G$2:$G$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -409,12 +409,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$10</f>
+              <f>'Chart'!$J$2:$J$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$10</f>
+              <f>'Chart'!$H$2:$H$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -445,12 +445,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$10</f>
+              <f>'Chart'!$J$2:$J$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$10</f>
+              <f>'Chart'!$I$2:$I$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -961,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1288,6 +1288,35 @@
       </c>
       <c r="I10" t="n">
         <v>17362.5652173913</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7532.272727272727</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4540.181818181818</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3522.454545454545</v>
+      </c>
+      <c r="E11" t="n">
+        <v>943.5454545454545</v>
+      </c>
+      <c r="F11" t="n">
+        <v>95.81818181818181</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>146.8636363636364</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16781.13636363636</v>
       </c>
     </row>
   </sheetData>
@@ -1302,7 +1331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1680,6 +1709,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7532.272727272727</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4540.181818181818</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3522.454545454545</v>
+      </c>
+      <c r="E11" t="n">
+        <v>943.5454545454545</v>
+      </c>
+      <c r="F11" t="n">
+        <v>95.81818181818181</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>146.8636363636364</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16781.13636363636</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.271842030418354</v>
+      </c>
+      <c r="K11" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1295,28 +1295,28 @@
         <v>46304</v>
       </c>
       <c r="B11" t="n">
-        <v>7532.272727272727</v>
+        <v>7532.130434782609</v>
       </c>
       <c r="C11" t="n">
-        <v>4540.181818181818</v>
+        <v>4542.260869565217</v>
       </c>
       <c r="D11" t="n">
-        <v>3522.454545454545</v>
+        <v>3502.173913043478</v>
       </c>
       <c r="E11" t="n">
-        <v>943.5454545454545</v>
+        <v>931.3478260869565</v>
       </c>
       <c r="F11" t="n">
-        <v>95.81818181818181</v>
+        <v>91.65217391304348</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>146.8636363636364</v>
+        <v>141.6521739130435</v>
       </c>
       <c r="I11" t="n">
-        <v>16781.13636363636</v>
+        <v>16741.21739130435</v>
       </c>
     </row>
   </sheetData>
@@ -1714,34 +1714,34 @@
         <v>46304</v>
       </c>
       <c r="B11" t="n">
-        <v>7532.272727272727</v>
+        <v>7532.130434782609</v>
       </c>
       <c r="C11" t="n">
-        <v>4540.181818181818</v>
+        <v>4542.260869565217</v>
       </c>
       <c r="D11" t="n">
-        <v>3522.454545454545</v>
+        <v>3502.173913043478</v>
       </c>
       <c r="E11" t="n">
-        <v>943.5454545454545</v>
+        <v>931.3478260869565</v>
       </c>
       <c r="F11" t="n">
-        <v>95.81818181818181</v>
+        <v>91.65217391304348</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>146.8636363636364</v>
+        <v>141.6521739130435</v>
       </c>
       <c r="I11" t="n">
-        <v>16781.13636363636</v>
+        <v>16741.21739130435</v>
       </c>
       <c r="J11" t="n">
-        <v>0.271842030418354</v>
+        <v>0.2703013650246203</v>
       </c>
       <c r="K11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -157,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>canada_ieso_generation_daily - Data (to Oct/26)</a:t>
+              <a:t>Ontario power generation by source (IESO, daily mean) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -165,8 +165,9 @@
       <overlay val="0"/>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -176,32 +177,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="008300"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="008300"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$11</f>
+              <f>'Chart'!$I$2:$I$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$11</f>
+              <f>'Chart'!$B$2:$B$12</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
@@ -212,32 +205,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$11</f>
+              <f>'Chart'!$I$2:$I$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$11</f>
+              <f>'Chart'!$C$2:$C$12</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="2"/>
@@ -248,32 +233,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$11</f>
+              <f>'Chart'!$I$2:$I$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$11</f>
+              <f>'Chart'!$D$2:$D$12</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="3"/>
@@ -284,32 +261,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$11</f>
+              <f>'Chart'!$I$2:$I$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$11</f>
+              <f>'Chart'!$E$2:$E$12</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="4"/>
@@ -320,32 +289,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="EDA100"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="EDA100"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$11</f>
+              <f>'Chart'!$I$2:$I$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$11</f>
+              <f>'Chart'!$F$2:$F$12</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="5"/>
@@ -356,32 +317,24 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="008300"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="008300"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$11</f>
+              <f>'Chart'!$I$2:$I$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$11</f>
+              <f>'Chart'!$G$2:$G$12</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="6"/>
@@ -392,72 +345,30 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="9A9A9A"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:srgbClr val="9A9A9A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$11</f>
+              <f>'Chart'!$I$2:$I$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$11</f>
+              <f>'Chart'!$H$2:$H$12</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!I1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:srgbClr val="E34948"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Chart'!$J$2:$J$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$I$2:$I$11</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
+        <gapWidth val="30"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -503,7 +414,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>MW (daily mean)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -541,7 +452,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -961,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -975,45 +886,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>NUCLEAR_MW</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>GAS_MW</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>HYDRO_MW</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>WIND_MW</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>SOLAR_MW</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>BIOFUEL_MW</t>
+          <t>Biofuel</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>OTHER_MW</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Total_MW</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Axis label</t>
         </is>
@@ -1044,10 +950,7 @@
       <c r="H2" t="n">
         <v>97.39130434782609</v>
       </c>
-      <c r="I2" t="n">
-        <v>17986.69565217392</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Sep/26</t>
         </is>
@@ -1078,10 +981,7 @@
       <c r="H3" t="n">
         <v>132.8260869565217</v>
       </c>
-      <c r="I3" t="n">
-        <v>18218.65217391304</v>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Oct/26</t>
         </is>
@@ -1112,9 +1012,6 @@
       <c r="H4" t="n">
         <v>115.5652173913043</v>
       </c>
-      <c r="I4" t="n">
-        <v>17858.60869565217</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1141,9 +1038,6 @@
       <c r="H5" t="n">
         <v>117.2083333333333</v>
       </c>
-      <c r="I5" t="n">
-        <v>15847.375</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1170,9 +1064,6 @@
       <c r="H6" t="n">
         <v>101.7826086956522</v>
       </c>
-      <c r="I6" t="n">
-        <v>16400</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1199,9 +1090,6 @@
       <c r="H7" t="n">
         <v>113.2608695652174</v>
       </c>
-      <c r="I7" t="n">
-        <v>16892.86956521739</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1228,9 +1116,6 @@
       <c r="H8" t="n">
         <v>116.3478260869565</v>
       </c>
-      <c r="I8" t="n">
-        <v>16487.91304347826</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1257,9 +1142,6 @@
       <c r="H9" t="n">
         <v>175.5652173913043</v>
       </c>
-      <c r="I9" t="n">
-        <v>17593.86956521739</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1286,9 +1168,6 @@
       <c r="H10" t="n">
         <v>171.0869565217391</v>
       </c>
-      <c r="I10" t="n">
-        <v>17362.5652173913</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1315,8 +1194,31 @@
       <c r="H11" t="n">
         <v>141.6521739130435</v>
       </c>
-      <c r="I11" t="n">
-        <v>16741.21739130435</v>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7509.727272727273</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3793.909090909091</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3243.590909090909</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2189.409090909091</v>
+      </c>
+      <c r="F12" t="n">
+        <v>78.45454545454545</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>80.13636363636364</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1744,6 +1646,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7509.727272727273</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3793.909090909091</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3243.590909090909</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2189.409090909091</v>
+      </c>
+      <c r="F12" t="n">
+        <v>78.45454545454545</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>80.13636363636364</v>
+      </c>
+      <c r="I12" t="n">
+        <v>16895.22727272727</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3262136967137034</v>
+      </c>
+      <c r="K12" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1200,25 +1200,25 @@
         <v>46305</v>
       </c>
       <c r="B12" t="n">
-        <v>7509.727272727273</v>
+        <v>7508.869565217391</v>
       </c>
       <c r="C12" t="n">
-        <v>3793.909090909091</v>
+        <v>3779.608695652174</v>
       </c>
       <c r="D12" t="n">
-        <v>3243.590909090909</v>
+        <v>3232.086956521739</v>
       </c>
       <c r="E12" t="n">
-        <v>2189.409090909091</v>
+        <v>2208.478260869565</v>
       </c>
       <c r="F12" t="n">
-        <v>78.45454545454545</v>
+        <v>75.04347826086956</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>80.13636363636364</v>
+        <v>76.69565217391305</v>
       </c>
     </row>
   </sheetData>
@@ -1651,34 +1651,34 @@
         <v>46305</v>
       </c>
       <c r="B12" t="n">
-        <v>7509.727272727273</v>
+        <v>7508.869565217391</v>
       </c>
       <c r="C12" t="n">
-        <v>3793.909090909091</v>
+        <v>3779.608695652174</v>
       </c>
       <c r="D12" t="n">
-        <v>3243.590909090909</v>
+        <v>3232.086956521739</v>
       </c>
       <c r="E12" t="n">
-        <v>2189.409090909091</v>
+        <v>2208.478260869565</v>
       </c>
       <c r="F12" t="n">
-        <v>78.45454545454545</v>
+        <v>75.04347826086956</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>80.13636363636364</v>
+        <v>76.69565217391305</v>
       </c>
       <c r="I12" t="n">
-        <v>16895.22727272727</v>
+        <v>16880.78260869565</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3262136967137034</v>
+        <v>0.32673892102674</v>
       </c>
       <c r="K12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -187,12 +187,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$12</f>
+              <f>'Chart'!$I$2:$I$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$12</f>
+              <f>'Chart'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -215,12 +215,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$12</f>
+              <f>'Chart'!$I$2:$I$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$12</f>
+              <f>'Chart'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$12</f>
+              <f>'Chart'!$I$2:$I$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$12</f>
+              <f>'Chart'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -271,12 +271,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$12</f>
+              <f>'Chart'!$I$2:$I$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$12</f>
+              <f>'Chart'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -299,12 +299,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$12</f>
+              <f>'Chart'!$I$2:$I$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$12</f>
+              <f>'Chart'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +327,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$12</f>
+              <f>'Chart'!$I$2:$I$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$12</f>
+              <f>'Chart'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -355,12 +355,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$I$2:$I$12</f>
+              <f>'Chart'!$I$2:$I$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$12</f>
+              <f>'Chart'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -872,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1219,6 +1219,32 @@
       </c>
       <c r="H12" t="n">
         <v>76.69565217391305</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7496.590909090909</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4336</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3322.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1295.318181818182</v>
+      </c>
+      <c r="F13" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>99.5</v>
       </c>
     </row>
   </sheetData>
@@ -1233,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1707,41 @@
         <v>23</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7496.590909090909</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4336</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3322.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1295.318181818182</v>
+      </c>
+      <c r="F13" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>16602.40909090909</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2813036443232499</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/canada_ieso_generation_daily.xlsx
@@ -1226,25 +1226,25 @@
         <v>46306</v>
       </c>
       <c r="B13" t="n">
-        <v>7496.590909090909</v>
+        <v>7495.913043478261</v>
       </c>
       <c r="C13" t="n">
-        <v>4336</v>
+        <v>4350.260869565217</v>
       </c>
       <c r="D13" t="n">
-        <v>3322.5</v>
+        <v>3312.565217391304</v>
       </c>
       <c r="E13" t="n">
-        <v>1295.318181818182</v>
+        <v>1253.695652173913</v>
       </c>
       <c r="F13" t="n">
-        <v>52.5</v>
+        <v>50.21739130434783</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>99.5</v>
+        <v>98.04347826086956</v>
       </c>
     </row>
   </sheetData>
@@ -1712,34 +1712,34 @@
         <v>46306</v>
       </c>
       <c r="B13" t="n">
-        <v>7496.590909090909</v>
+        <v>7495.913043478261</v>
       </c>
       <c r="C13" t="n">
-        <v>4336</v>
+        <v>4350.260869565217</v>
       </c>
       <c r="D13" t="n">
-        <v>3322.5</v>
+        <v>3312.565217391304</v>
       </c>
       <c r="E13" t="n">
-        <v>1295.318181818182</v>
+        <v>1253.695652173913</v>
       </c>
       <c r="F13" t="n">
-        <v>52.5</v>
+        <v>50.21739130434783</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>99.5</v>
+        <v>98.04347826086956</v>
       </c>
       <c r="I13" t="n">
-        <v>16602.40909090909</v>
+        <v>16560.69565217391</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2813036443232499</v>
+        <v>0.2787611316474839</v>
       </c>
       <c r="K13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
